--- a/Учет_вагонов_шаблон.xlsx
+++ b/Учет_вагонов_шаблон.xlsx
@@ -857,7 +857,7 @@
       <c r="F2" s="3" t="n"/>
       <c r="G2" s="3" t="n"/>
       <c r="H2" s="3">
-        <f>XLOOKUP([@[Дата фиксации цены]],tblКурсы[Дата],tblКурсы[Курс],,-1)</f>
+        <f>LOOKUP([@[Дата фиксации цены]],tblКурсы[Дата],tblКурсы[Курс])</f>
         <v/>
       </c>
       <c r="I2" s="3">
@@ -921,7 +921,7 @@
         <v/>
       </c>
       <c r="X2" s="4">
-        <f>IFERROR(MAXIFS(tblПлатежи[Дата платежа],tblПлатежи[ID вагона],[@[ID вагона]],tblПлатежи[Статус],"факт"),"")</f>
+        <f>IFERROR(SUMPRODUCT(MAX((tblПлатежи[ID вагона]=[@[ID вагона]])*(tblПлатежи[Статус]="факт")*(tblПлатежи[Дата платежа]))),"")</f>
         <v/>
       </c>
       <c r="Y2" s="4" t="n"/>
@@ -1015,7 +1015,7 @@
       <c r="A2" s="4" t="n"/>
       <c r="C2" s="3" t="n"/>
       <c r="E2" s="2">
-        <f>XLOOKUP([@[Дата платежа]],tblКурсы[Дата],tblКурсы[Курс],,-1)</f>
+        <f>LOOKUP([@[Дата платежа]],tblКурсы[Дата],tblКурсы[Курс])</f>
         <v/>
       </c>
       <c r="F2" s="3">
@@ -1027,7 +1027,7 @@
         <v/>
       </c>
       <c r="J2">
-        <f>COUNTIF($B$2:[@[ID вагона]],[@[ID вагона]])</f>
+        <f>COUNTIF(INDEX(tblПлатежи[ID вагона],1):[@[ID вагона]],[@[ID вагона]])</f>
         <v/>
       </c>
     </row>
